--- a/SFN/precuneus activation mask/precuniusXage.xlsx
+++ b/SFN/precuneus activation mask/precuniusXage.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/avidachs/Documents/GitHub/rf1-sra-trust/SFN/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/avidachs/Documents/GitHub/rf1-sra-trust/SFN/precuneus activation mask/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F699854C-BA69-534C-9B45-1682ABD1A0B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01929802-0586-174D-B5F4-CA5385B2746B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="180" yWindow="1000" windowWidth="27640" windowHeight="15620" xr2:uid="{EB55BB5A-77F1-6843-8992-4F8ABCDB01C9}"/>
   </bookViews>
